--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.01185640790814534</v>
       </c>
       <c r="C2" t="n">
-        <v>86978808</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>86978808</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>58690372</v>
+        <v>4691403</v>
       </c>
       <c r="L2" t="n">
-        <v>33093825</v>
+        <v>2934668</v>
       </c>
       <c r="M2" t="n">
-        <v>8217576</v>
+        <v>786519</v>
       </c>
       <c r="N2" t="n">
-        <v>449887</v>
+        <v>48178</v>
       </c>
       <c r="O2" t="n">
-        <v>4958464</v>
+        <v>458774</v>
       </c>
       <c r="P2" t="n">
-        <v>2030353</v>
+        <v>179344</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999116063117981</v>
+        <v>0.9999930858612061</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8546743988990784</v>
+        <v>0.9566615223884583</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7238894104957581</v>
+        <v>0.8987423777580261</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6405664086341858</v>
+        <v>0.8572245836257935</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4723957180976868</v>
+        <v>0.703955352306366</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6949599385261536</v>
+        <v>0.8999009132385254</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7529025077819824</v>
+        <v>0.9312410950660706</v>
       </c>
       <c r="X2" t="n">
-        <v>86978808</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>86978808</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>57239945</v>
+        <v>4535637</v>
       </c>
       <c r="AG2" t="n">
-        <v>30676347</v>
+        <v>2682458</v>
       </c>
       <c r="AH2" t="n">
-        <v>7468430</v>
+        <v>705093</v>
       </c>
       <c r="AI2" t="n">
-        <v>414207</v>
+        <v>45132</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4561702</v>
+        <v>418529</v>
       </c>
       <c r="AK2" t="n">
-        <v>1909979</v>
+        <v>168879</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8280243873596191</v>
+        <v>0.9185657501220703</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6838664412498474</v>
+        <v>0.8371988534927368</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.576022744178772</v>
+        <v>0.7613507509231567</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3347689807415009</v>
+        <v>0.5106700658798218</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.641340970993042</v>
+        <v>0.8237884044647217</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7059140801429749</v>
+        <v>0.8738299608230591</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002885758895481184</v>
       </c>
       <c r="C3" t="n">
-        <v>2462</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>58690372</v>
+        <v>4691403</v>
       </c>
       <c r="E3" t="n">
-        <v>8986562</v>
+        <v>224592</v>
       </c>
       <c r="F3" t="n">
-        <v>531640</v>
+        <v>6989</v>
       </c>
       <c r="G3" t="n">
-        <v>62299</v>
+        <v>1713</v>
       </c>
       <c r="H3" t="n">
-        <v>54432</v>
+        <v>54</v>
       </c>
       <c r="I3" t="n">
-        <v>8955</v>
+        <v>26</v>
       </c>
       <c r="J3" t="n">
-        <v>137999102</v>
+        <v>9857585</v>
       </c>
       <c r="K3" t="n">
-        <v>146669389</v>
+        <v>10933091</v>
       </c>
       <c r="L3" t="n">
-        <v>166852943</v>
+        <v>12525607</v>
       </c>
       <c r="M3" t="n">
-        <v>207307740</v>
+        <v>15011213</v>
       </c>
       <c r="N3" t="n">
-        <v>223238378</v>
+        <v>15961587</v>
       </c>
       <c r="O3" t="n">
-        <v>215669621</v>
+        <v>15510699</v>
       </c>
       <c r="P3" t="n">
-        <v>221610112</v>
+        <v>15863876</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8588408827781677</v>
+        <v>0.9526116847991943</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7271802425384521</v>
+        <v>0.9130446910858154</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6288884282112122</v>
+        <v>0.8473703861236572</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3614255487918854</v>
+        <v>0.5440645217895508</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6945064067840576</v>
+        <v>0.9019088745117188</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7494455575942993</v>
+        <v>0.9278877377510071</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57239945</v>
+        <v>4535637</v>
       </c>
       <c r="Z3" t="n">
-        <v>10080516</v>
+        <v>363917</v>
       </c>
       <c r="AA3" t="n">
-        <v>723422</v>
+        <v>14825</v>
       </c>
       <c r="AB3" t="n">
-        <v>208028</v>
+        <v>10241</v>
       </c>
       <c r="AC3" t="n">
-        <v>71702</v>
+        <v>106</v>
       </c>
       <c r="AD3" t="n">
-        <v>13109</v>
+        <v>54</v>
       </c>
       <c r="AE3" t="n">
-        <v>138006792</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>144760491</v>
+        <v>10743519</v>
       </c>
       <c r="AG3" t="n">
-        <v>165294934</v>
+        <v>12334615</v>
       </c>
       <c r="AH3" t="n">
-        <v>206421691</v>
+        <v>14921197</v>
       </c>
       <c r="AI3" t="n">
-        <v>222917758</v>
+        <v>15938602</v>
       </c>
       <c r="AJ3" t="n">
-        <v>215294995</v>
+        <v>15472205</v>
       </c>
       <c r="AK3" t="n">
-        <v>221480757</v>
+        <v>15852734</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8376162052154541</v>
+        <v>0.9209826588630676</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6740603446960449</v>
+        <v>0.8345761895179749</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5715565085411072</v>
+        <v>0.759644627571106</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3327613472938538</v>
+        <v>0.5096666216850281</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6389340162277222</v>
+        <v>0.822790801525116</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7050130367279053</v>
+        <v>0.8737440705299377</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03944238488751694</v>
       </c>
       <c r="C4" t="n">
-        <v>952</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>9195950</v>
+        <v>198522</v>
       </c>
       <c r="E4" t="n">
-        <v>33093825</v>
+        <v>2934668</v>
       </c>
       <c r="F4" t="n">
-        <v>2617340</v>
+        <v>77814</v>
       </c>
       <c r="G4" t="n">
-        <v>110639</v>
+        <v>1915</v>
       </c>
       <c r="H4" t="n">
-        <v>425381</v>
+        <v>1178</v>
       </c>
       <c r="I4" t="n">
-        <v>65708</v>
+        <v>56</v>
       </c>
       <c r="J4" t="n">
-        <v>7690</v>
+        <v>43</v>
       </c>
       <c r="K4" t="n">
-        <v>9979489</v>
+        <v>212529</v>
       </c>
       <c r="L4" t="n">
-        <v>12622862</v>
+        <v>330637</v>
       </c>
       <c r="M4" t="n">
-        <v>4611033</v>
+        <v>130999</v>
       </c>
       <c r="N4" t="n">
-        <v>502465</v>
+        <v>20261</v>
       </c>
       <c r="O4" t="n">
-        <v>2176428</v>
+        <v>51031</v>
       </c>
       <c r="P4" t="n">
-        <v>666348</v>
+        <v>13242</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999558329582214</v>
+        <v>0.999996542930603</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8567525744438171</v>
+        <v>0.9546323418617249</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7255311012268066</v>
+        <v>0.9058370590209961</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6346737146377563</v>
+        <v>0.8522689938545227</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4095263183116913</v>
+        <v>0.6137676239013672</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6947331428527832</v>
+        <v>0.9009038209915161</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7511700987815857</v>
+        <v>0.9295613765716553</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>10897826</v>
+        <v>380423</v>
       </c>
       <c r="Z4" t="n">
-        <v>30676347</v>
+        <v>2682458</v>
       </c>
       <c r="AA4" t="n">
-        <v>3124754</v>
+        <v>135949</v>
       </c>
       <c r="AB4" t="n">
-        <v>213183</v>
+        <v>8964</v>
       </c>
       <c r="AC4" t="n">
-        <v>514301</v>
+        <v>5960</v>
       </c>
       <c r="AD4" t="n">
-        <v>83384</v>
+        <v>402</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>11888387</v>
+        <v>402101</v>
       </c>
       <c r="AG4" t="n">
-        <v>14180871</v>
+        <v>521629</v>
       </c>
       <c r="AH4" t="n">
-        <v>5497082</v>
+        <v>221015</v>
       </c>
       <c r="AI4" t="n">
-        <v>823085</v>
+        <v>43246</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2551054</v>
+        <v>89525</v>
       </c>
       <c r="AK4" t="n">
-        <v>795703</v>
+        <v>24384</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8327926397323608</v>
+        <v>0.9197726845741272</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6789279580116272</v>
+        <v>0.8358854055404663</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5737809538841248</v>
+        <v>0.7604967355728149</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3337621688842773</v>
+        <v>0.5101678967475891</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6401352286338806</v>
+        <v>0.8232892751693726</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7054632902145386</v>
+        <v>0.873786985874176</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1454</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>558342</v>
+        <v>7854</v>
       </c>
       <c r="E5" t="n">
-        <v>2895922</v>
+        <v>95079</v>
       </c>
       <c r="F5" t="n">
-        <v>8217576</v>
+        <v>786519</v>
       </c>
       <c r="G5" t="n">
-        <v>180059</v>
+        <v>8941</v>
       </c>
       <c r="H5" t="n">
-        <v>1059067</v>
+        <v>29185</v>
       </c>
       <c r="I5" t="n">
-        <v>154407</v>
+        <v>606</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9646350</v>
+        <v>233377</v>
       </c>
       <c r="L5" t="n">
-        <v>12415970</v>
+        <v>279488</v>
       </c>
       <c r="M5" t="n">
-        <v>4849251</v>
+        <v>141669</v>
       </c>
       <c r="N5" t="n">
-        <v>794870</v>
+        <v>40374</v>
       </c>
       <c r="O5" t="n">
-        <v>2181087</v>
+        <v>49896</v>
       </c>
       <c r="P5" t="n">
-        <v>678787</v>
+        <v>13938</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999658465385437</v>
+        <v>0.9999973177909851</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9127684831619263</v>
+        <v>0.9722529649734497</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8887091875076294</v>
+        <v>0.9620342254638672</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9579516053199768</v>
+        <v>0.9830328822135925</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9942336678504944</v>
+        <v>0.9962269067764282</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9806320071220398</v>
+        <v>0.9937196969985962</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9940212368965149</v>
+        <v>0.9983087182044983</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>705306</v>
+        <v>12213</v>
       </c>
       <c r="Z5" t="n">
-        <v>3245096</v>
+        <v>143254</v>
       </c>
       <c r="AA5" t="n">
-        <v>7468430</v>
+        <v>705093</v>
       </c>
       <c r="AB5" t="n">
-        <v>225325</v>
+        <v>13468</v>
       </c>
       <c r="AC5" t="n">
-        <v>1236366</v>
+        <v>51713</v>
       </c>
       <c r="AD5" t="n">
-        <v>186304</v>
+        <v>2447</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>11096777</v>
+        <v>389143</v>
       </c>
       <c r="AG5" t="n">
-        <v>14833448</v>
+        <v>531698</v>
       </c>
       <c r="AH5" t="n">
-        <v>5598397</v>
+        <v>223095</v>
       </c>
       <c r="AI5" t="n">
-        <v>830550</v>
+        <v>43420</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2577849</v>
+        <v>90141</v>
       </c>
       <c r="AK5" t="n">
-        <v>799161</v>
+        <v>24403</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8978371620178223</v>
+        <v>0.9507638812065125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8710392117500305</v>
+        <v>0.9344554543495178</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.95068359375</v>
+        <v>0.9723647236824036</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.992650032043457</v>
+        <v>0.9946070909500122</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9772034287452698</v>
+        <v>0.9888200759887695</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9929112792015076</v>
+        <v>0.996964156627655</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1897</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>158591</v>
+        <v>6124</v>
       </c>
       <c r="E6" t="n">
-        <v>220712</v>
+        <v>10055</v>
       </c>
       <c r="F6" t="n">
-        <v>251413</v>
+        <v>16253</v>
       </c>
       <c r="G6" t="n">
-        <v>449887</v>
+        <v>48178</v>
       </c>
       <c r="H6" t="n">
-        <v>137589</v>
+        <v>7367</v>
       </c>
       <c r="I6" t="n">
-        <v>24668</v>
+        <v>559</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>191305</v>
+        <v>9406</v>
       </c>
       <c r="Z6" t="n">
-        <v>223878</v>
+        <v>9011</v>
       </c>
       <c r="AA6" t="n">
-        <v>231352</v>
+        <v>14794</v>
       </c>
       <c r="AB6" t="n">
-        <v>414207</v>
+        <v>45132</v>
       </c>
       <c r="AC6" t="n">
-        <v>155451</v>
+        <v>9330</v>
       </c>
       <c r="AD6" t="n">
-        <v>28564</v>
+        <v>879</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>595</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>62005</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>468785</v>
+        <v>815</v>
       </c>
       <c r="F7" t="n">
-        <v>1107158</v>
+        <v>29619</v>
       </c>
       <c r="G7" t="n">
-        <v>129934</v>
+        <v>7456</v>
       </c>
       <c r="H7" t="n">
-        <v>4958464</v>
+        <v>458774</v>
       </c>
       <c r="I7" t="n">
-        <v>412610</v>
+        <v>11995</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>86233</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>567154</v>
+        <v>5213</v>
       </c>
       <c r="AA7" t="n">
-        <v>1287679</v>
+        <v>54236</v>
       </c>
       <c r="AB7" t="n">
-        <v>152441</v>
+        <v>10075</v>
       </c>
       <c r="AC7" t="n">
-        <v>4561702</v>
+        <v>418529</v>
       </c>
       <c r="AD7" t="n">
-        <v>484342</v>
+        <v>20602</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>330</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>4601</v>
+        <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>50881</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>103482</v>
+        <v>324</v>
       </c>
       <c r="G8" t="n">
-        <v>19534</v>
+        <v>236</v>
       </c>
       <c r="H8" t="n">
-        <v>499959</v>
+        <v>13247</v>
       </c>
       <c r="I8" t="n">
-        <v>2030353</v>
+        <v>179344</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>7717</v>
+        <v>44</v>
       </c>
       <c r="Z8" t="n">
-        <v>64227</v>
+        <v>234</v>
       </c>
       <c r="AA8" t="n">
-        <v>129875</v>
+        <v>1211</v>
       </c>
       <c r="AB8" t="n">
-        <v>24108</v>
+        <v>498</v>
       </c>
       <c r="AC8" t="n">
-        <v>573234</v>
+        <v>22416</v>
       </c>
       <c r="AD8" t="n">
-        <v>1909979</v>
+        <v>168879</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
